--- a/codigos/codigos_flavio.xlsx
+++ b/codigos/codigos_flavio.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E697"/>
+  <dimension ref="A1:F697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Repuesto</t>
+          <t>Descripcion</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -435,6 +435,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Articulo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Codigos</t>
         </is>
       </c>
     </row>
@@ -458,6 +463,11 @@
       <c r="E2" t="n">
         <v>3</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>002.00003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -479,6 +489,11 @@
       <c r="E3" t="n">
         <v>4</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>002.00004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -500,6 +515,11 @@
       <c r="E4" t="n">
         <v>6</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>002.00006</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -521,6 +541,11 @@
       <c r="E5" t="n">
         <v>17</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>002.00017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -542,6 +567,11 @@
       <c r="E6" t="n">
         <v>23</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>002.00023</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -563,6 +593,11 @@
       <c r="E7" t="n">
         <v>24</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>002.00024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -584,6 +619,11 @@
       <c r="E8" t="n">
         <v>26</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>002.00026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -605,6 +645,11 @@
       <c r="E9" t="n">
         <v>27</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>002.00027</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -626,6 +671,11 @@
       <c r="E10" t="n">
         <v>48</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>002.00048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -647,6 +697,11 @@
       <c r="E11" t="n">
         <v>51</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>002.00051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -668,6 +723,11 @@
       <c r="E12" t="n">
         <v>52</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>002.00052</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -689,6 +749,11 @@
       <c r="E13" t="n">
         <v>54</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>002.00054</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -710,6 +775,11 @@
       <c r="E14" t="n">
         <v>57</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>002.00057</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -731,6 +801,11 @@
       <c r="E15" t="n">
         <v>59</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>002.00059</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -752,6 +827,11 @@
       <c r="E16" t="n">
         <v>11</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>003.00011</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -773,6 +853,11 @@
       <c r="E17" t="n">
         <v>6</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>004.00006</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -794,6 +879,11 @@
       <c r="E18" t="n">
         <v>11</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>004.00011</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -815,6 +905,11 @@
       <c r="E19" t="n">
         <v>14</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>004.00014</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -836,6 +931,11 @@
       <c r="E20" t="n">
         <v>1</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>005.00001</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -857,6 +957,11 @@
       <c r="E21" t="n">
         <v>3</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>005.00003</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -878,6 +983,11 @@
       <c r="E22" t="n">
         <v>8</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>005.00008</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -899,6 +1009,11 @@
       <c r="E23" t="n">
         <v>9</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>005.00009</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -920,6 +1035,11 @@
       <c r="E24" t="n">
         <v>12</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>005.00012</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -941,6 +1061,11 @@
       <c r="E25" t="n">
         <v>29</v>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>005.00029</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -962,6 +1087,11 @@
       <c r="E26" t="n">
         <v>32</v>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>005.00032</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -983,6 +1113,11 @@
       <c r="E27" t="n">
         <v>34</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>005.00034</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1004,6 +1139,11 @@
       <c r="E28" t="n">
         <v>35</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>005.00035</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1025,6 +1165,11 @@
       <c r="E29" t="n">
         <v>36</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>005.00036</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1046,6 +1191,11 @@
       <c r="E30" t="n">
         <v>52</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>005.00052</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1067,6 +1217,11 @@
       <c r="E31" t="n">
         <v>57</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>005.00057</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1088,6 +1243,11 @@
       <c r="E32" t="n">
         <v>59</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>005.00059</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1109,6 +1269,11 @@
       <c r="E33" t="n">
         <v>62</v>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>005.00062</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1130,6 +1295,11 @@
       <c r="E34" t="n">
         <v>71</v>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>005.00071</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1151,6 +1321,11 @@
       <c r="E35" t="n">
         <v>75</v>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>005.00075</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1172,6 +1347,11 @@
       <c r="E36" t="n">
         <v>78</v>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>005.00078</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1193,6 +1373,11 @@
       <c r="E37" t="n">
         <v>87</v>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>005.00087</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1214,6 +1399,11 @@
       <c r="E38" t="n">
         <v>92</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>005.00092</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1235,6 +1425,11 @@
       <c r="E39" t="n">
         <v>93</v>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>005.00093</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1256,6 +1451,11 @@
       <c r="E40" t="n">
         <v>112</v>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>005.00112</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1277,6 +1477,11 @@
       <c r="E41" t="n">
         <v>118</v>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>005.00118</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1298,6 +1503,11 @@
       <c r="E42" t="n">
         <v>122</v>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>005.00122</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1319,6 +1529,11 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>007.00001</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1340,6 +1555,11 @@
       <c r="E44" t="n">
         <v>89</v>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>007.00089</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1361,6 +1581,11 @@
       <c r="E45" t="n">
         <v>92</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>007.00092</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1382,6 +1607,11 @@
       <c r="E46" t="n">
         <v>2</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>008.00002</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1403,6 +1633,11 @@
       <c r="E47" t="n">
         <v>2</v>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>008.00002</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1424,6 +1659,11 @@
       <c r="E48" t="n">
         <v>4</v>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>008.00004</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1445,6 +1685,11 @@
       <c r="E49" t="n">
         <v>7</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>008.00007</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1466,6 +1711,11 @@
       <c r="E50" t="n">
         <v>8</v>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>008.00008</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1487,6 +1737,11 @@
       <c r="E51" t="n">
         <v>9</v>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>008.00009</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1508,6 +1763,11 @@
       <c r="E52" t="n">
         <v>9</v>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>008.00009</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1529,6 +1789,11 @@
       <c r="E53" t="n">
         <v>12</v>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>008.00012</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1550,6 +1815,11 @@
       <c r="E54" t="n">
         <v>13</v>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>008.00013</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1571,6 +1841,11 @@
       <c r="E55" t="n">
         <v>14</v>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>008.00014</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1592,6 +1867,11 @@
       <c r="E56" t="n">
         <v>15</v>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>008.00015</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1613,6 +1893,11 @@
       <c r="E57" t="n">
         <v>16</v>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>008.00016</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1634,6 +1919,11 @@
       <c r="E58" t="n">
         <v>18</v>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>008.00018</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1655,6 +1945,11 @@
       <c r="E59" t="n">
         <v>19</v>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>008.00019</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1676,6 +1971,11 @@
       <c r="E60" t="n">
         <v>22</v>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>008.00022</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1697,6 +1997,11 @@
       <c r="E61" t="n">
         <v>22</v>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>008.00022</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1718,6 +2023,11 @@
       <c r="E62" t="n">
         <v>27</v>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>008.00027</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1739,6 +2049,11 @@
       <c r="E63" t="n">
         <v>28</v>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>008.00028</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1760,6 +2075,11 @@
       <c r="E64" t="n">
         <v>36</v>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>008.00036</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1781,6 +2101,11 @@
       <c r="E65" t="n">
         <v>61</v>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>008.00061</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1802,6 +2127,11 @@
       <c r="E66" t="n">
         <v>62</v>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>008.00062</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1823,6 +2153,11 @@
       <c r="E67" t="n">
         <v>63</v>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>008.00063</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1844,6 +2179,11 @@
       <c r="E68" t="n">
         <v>64</v>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>008.00064</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1865,6 +2205,11 @@
       <c r="E69" t="n">
         <v>66</v>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>008.00066</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1886,6 +2231,11 @@
       <c r="E70" t="n">
         <v>93</v>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>008.00093</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1907,6 +2257,11 @@
       <c r="E71" t="n">
         <v>98</v>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>008.00098</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1928,6 +2283,11 @@
       <c r="E72" t="n">
         <v>99</v>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>008.00099</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1949,6 +2309,11 @@
       <c r="E73" t="n">
         <v>103</v>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>008.00103</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1970,6 +2335,11 @@
       <c r="E74" t="n">
         <v>104</v>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>008.00104</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1991,6 +2361,11 @@
       <c r="E75" t="n">
         <v>108</v>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>008.00108</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2012,6 +2387,11 @@
       <c r="E76" t="n">
         <v>112</v>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>008.00112</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2033,6 +2413,11 @@
       <c r="E77" t="n">
         <v>113</v>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>008.00113</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2054,6 +2439,11 @@
       <c r="E78" t="n">
         <v>116</v>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>008.00116</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2075,6 +2465,11 @@
       <c r="E79" t="n">
         <v>117</v>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>008.00117</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2096,6 +2491,11 @@
       <c r="E80" t="n">
         <v>125</v>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>008.00125</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2117,6 +2517,11 @@
       <c r="E81" t="n">
         <v>131</v>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>008.00131</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2138,6 +2543,11 @@
       <c r="E82" t="n">
         <v>132</v>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>008.00132</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2159,6 +2569,11 @@
       <c r="E83" t="n">
         <v>134</v>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>008.00134</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2180,6 +2595,11 @@
       <c r="E84" t="n">
         <v>137</v>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>008.00137</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2201,6 +2621,11 @@
       <c r="E85" t="n">
         <v>138</v>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>008.00138</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2222,6 +2647,11 @@
       <c r="E86" t="n">
         <v>139</v>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>008.00139</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2243,6 +2673,11 @@
       <c r="E87" t="n">
         <v>141</v>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>008.00141</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2264,6 +2699,11 @@
       <c r="E88" t="n">
         <v>142</v>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>008.00142</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2285,6 +2725,11 @@
       <c r="E89" t="n">
         <v>143</v>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>008.00143</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2306,6 +2751,11 @@
       <c r="E90" t="n">
         <v>144</v>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>008.00144</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2327,6 +2777,11 @@
       <c r="E91" t="n">
         <v>145</v>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>008.00145</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2348,6 +2803,11 @@
       <c r="E92" t="n">
         <v>146</v>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>008.00146</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2369,6 +2829,11 @@
       <c r="E93" t="n">
         <v>151</v>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>008.00151</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2390,6 +2855,11 @@
       <c r="E94" t="n">
         <v>152</v>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>008.00152</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2411,6 +2881,11 @@
       <c r="E95" t="n">
         <v>153</v>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>008.00153</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2432,6 +2907,11 @@
       <c r="E96" t="n">
         <v>154</v>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>008.00154</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2453,6 +2933,11 @@
       <c r="E97" t="n">
         <v>157</v>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>008.00157</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2474,6 +2959,11 @@
       <c r="E98" t="n">
         <v>161</v>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>008.00161</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2495,6 +2985,11 @@
       <c r="E99" t="n">
         <v>162</v>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>008.00162</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2516,6 +3011,11 @@
       <c r="E100" t="n">
         <v>163</v>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>008.00163</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2537,6 +3037,11 @@
       <c r="E101" t="n">
         <v>164</v>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>008.00164</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2558,6 +3063,11 @@
       <c r="E102" t="n">
         <v>165</v>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>008.00165</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2579,6 +3089,11 @@
       <c r="E103" t="n">
         <v>169</v>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>008.00169</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2600,6 +3115,11 @@
       <c r="E104" t="n">
         <v>172</v>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>008.00172</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2621,6 +3141,11 @@
       <c r="E105" t="n">
         <v>176</v>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>008.00176</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2642,6 +3167,11 @@
       <c r="E106" t="n">
         <v>178</v>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>008.00178</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2663,6 +3193,11 @@
       <c r="E107" t="n">
         <v>185</v>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>008.00185</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2684,6 +3219,11 @@
       <c r="E108" t="n">
         <v>186</v>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>008.00186</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2705,6 +3245,11 @@
       <c r="E109" t="n">
         <v>188</v>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>008.00188</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2726,6 +3271,11 @@
       <c r="E110" t="n">
         <v>191</v>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>008.00191</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2747,6 +3297,11 @@
       <c r="E111" t="n">
         <v>195</v>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>008.00195</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2768,6 +3323,11 @@
       <c r="E112" t="n">
         <v>196</v>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>008.00196</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2789,6 +3349,11 @@
       <c r="E113" t="n">
         <v>198</v>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>008.00198</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2810,6 +3375,11 @@
       <c r="E114" t="n">
         <v>201</v>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>008.00201</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2831,6 +3401,11 @@
       <c r="E115" t="n">
         <v>202</v>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>008.00202</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2852,6 +3427,11 @@
       <c r="E116" t="n">
         <v>209</v>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>008.00209</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2873,6 +3453,11 @@
       <c r="E117" t="n">
         <v>211</v>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>008.00211</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2894,6 +3479,11 @@
       <c r="E118" t="n">
         <v>212</v>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>008.00212</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2915,6 +3505,11 @@
       <c r="E119" t="n">
         <v>213</v>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>008.00213</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2936,6 +3531,11 @@
       <c r="E120" t="n">
         <v>214</v>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>008.00214</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2957,6 +3557,11 @@
       <c r="E121" t="n">
         <v>216</v>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>008.00216</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2978,6 +3583,11 @@
       <c r="E122" t="n">
         <v>223</v>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>008.00223</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2999,6 +3609,11 @@
       <c r="E123" t="n">
         <v>224</v>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>008.00224</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3020,6 +3635,11 @@
       <c r="E124" t="n">
         <v>225</v>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>008.00225</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3041,6 +3661,11 @@
       <c r="E125" t="n">
         <v>226</v>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>008.00226</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3062,6 +3687,11 @@
       <c r="E126" t="n">
         <v>227</v>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>008.00227</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3083,6 +3713,11 @@
       <c r="E127" t="n">
         <v>228</v>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>008.00228</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3104,6 +3739,11 @@
       <c r="E128" t="n">
         <v>236</v>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>008.00236</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3125,6 +3765,11 @@
       <c r="E129" t="n">
         <v>237</v>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>008.00237</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3146,6 +3791,11 @@
       <c r="E130" t="n">
         <v>239</v>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>008.00239</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3167,6 +3817,11 @@
       <c r="E131" t="n">
         <v>243</v>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>008.00243</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3188,6 +3843,11 @@
       <c r="E132" t="n">
         <v>246</v>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>008.00246</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3209,6 +3869,11 @@
       <c r="E133" t="n">
         <v>264</v>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>008.00264</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3230,6 +3895,11 @@
       <c r="E134" t="n">
         <v>265</v>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>008.00265</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3251,6 +3921,11 @@
       <c r="E135" t="n">
         <v>268</v>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>008.00268</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3272,6 +3947,11 @@
       <c r="E136" t="n">
         <v>269</v>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>008.00269</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3293,6 +3973,11 @@
       <c r="E137" t="n">
         <v>271</v>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>008.00271</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3314,6 +3999,11 @@
       <c r="E138" t="n">
         <v>1</v>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>011.00001</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3335,6 +4025,11 @@
       <c r="E139" t="n">
         <v>221</v>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>013.00221</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3356,6 +4051,11 @@
       <c r="E140" t="n">
         <v>2</v>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>014.00002</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3377,6 +4077,11 @@
       <c r="E141" t="n">
         <v>4</v>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>014.00004</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3398,6 +4103,11 @@
       <c r="E142" t="n">
         <v>11</v>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>014.00011</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3419,6 +4129,11 @@
       <c r="E143" t="n">
         <v>12</v>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>014.00012</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3440,6 +4155,11 @@
       <c r="E144" t="n">
         <v>13</v>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>014.00013</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3461,6 +4181,11 @@
       <c r="E145" t="n">
         <v>13</v>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>014.00013</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3482,6 +4207,11 @@
       <c r="E146" t="n">
         <v>32</v>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>014.00032</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3503,6 +4233,11 @@
       <c r="E147" t="n">
         <v>34</v>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>014.00034</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3524,6 +4259,11 @@
       <c r="E148" t="n">
         <v>35</v>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>014.00035</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3545,6 +4285,11 @@
       <c r="E149" t="n">
         <v>78</v>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>014.00078</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3566,6 +4311,11 @@
       <c r="E150" t="n">
         <v>121</v>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>014.00121</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3587,6 +4337,11 @@
       <c r="E151" t="n">
         <v>122</v>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>014.00122</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3608,6 +4363,11 @@
       <c r="E152" t="n">
         <v>123</v>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>014.00123</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3629,6 +4389,11 @@
       <c r="E153" t="n">
         <v>128</v>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>014.00128</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3650,6 +4415,11 @@
       <c r="E154" t="n">
         <v>129</v>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>014.00129</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3671,6 +4441,11 @@
       <c r="E155" t="n">
         <v>133</v>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>014.00133</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3692,6 +4467,11 @@
       <c r="E156" t="n">
         <v>138</v>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>014.00138</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3713,6 +4493,11 @@
       <c r="E157" t="n">
         <v>141</v>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>014.00141</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3734,6 +4519,11 @@
       <c r="E158" t="n">
         <v>146</v>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>014.00146</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3755,6 +4545,11 @@
       <c r="E159" t="n">
         <v>188</v>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>014.00188</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3776,6 +4571,11 @@
       <c r="E160" t="n">
         <v>388</v>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>014.00388</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3797,6 +4597,11 @@
       <c r="E161" t="n">
         <v>392</v>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>014.00392</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3818,6 +4623,11 @@
       <c r="E162" t="n">
         <v>477</v>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>014.00477</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3839,6 +4649,11 @@
       <c r="E163" t="n">
         <v>478</v>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>014.00478</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3860,6 +4675,11 @@
       <c r="E164" t="n">
         <v>488</v>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>014.00488</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3881,6 +4701,11 @@
       <c r="E165" t="n">
         <v>492</v>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>014.00492</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3902,6 +4727,11 @@
       <c r="E166" t="n">
         <v>116</v>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>041.00116</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3923,6 +4753,11 @@
       <c r="E167" t="n">
         <v>1</v>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>051.00001</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3944,6 +4779,11 @@
       <c r="E168" t="n">
         <v>1</v>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>051.00001</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3965,6 +4805,11 @@
       <c r="E169" t="n">
         <v>8</v>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>056.00008</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3986,6 +4831,11 @@
       <c r="E170" t="n">
         <v>5</v>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>094.00005</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4007,6 +4857,11 @@
       <c r="E171" t="n">
         <v>7</v>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>094.00007</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4028,6 +4883,11 @@
       <c r="E172" t="n">
         <v>8</v>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>094.00008</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4049,6 +4909,11 @@
       <c r="E173" t="n">
         <v>18</v>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>094.00018</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4070,6 +4935,11 @@
       <c r="E174" t="n">
         <v>53</v>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>094.00053</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4091,6 +4961,11 @@
       <c r="E175" t="n">
         <v>67</v>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>094.00067</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4112,6 +4987,11 @@
       <c r="E176" t="n">
         <v>73</v>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>094.00073</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4133,6 +5013,11 @@
       <c r="E177" t="n">
         <v>74</v>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>094.00074</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4154,6 +5039,11 @@
       <c r="E178" t="n">
         <v>75</v>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>094.00075</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4175,6 +5065,11 @@
       <c r="E179" t="n">
         <v>81</v>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>094.00081</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4196,6 +5091,11 @@
       <c r="E180" t="n">
         <v>82</v>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>094.00082</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4217,6 +5117,11 @@
       <c r="E181" t="n">
         <v>86</v>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>094.00086</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4238,6 +5143,11 @@
       <c r="E182" t="n">
         <v>87</v>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>094.00087</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4259,6 +5169,11 @@
       <c r="E183" t="n">
         <v>104</v>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>094.00104</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4280,6 +5195,11 @@
       <c r="E184" t="n">
         <v>105</v>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>094.00105</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4301,6 +5221,11 @@
       <c r="E185" t="n">
         <v>109</v>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>094.00109</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4322,6 +5247,11 @@
       <c r="E186" t="n">
         <v>116</v>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>094.00116</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4343,6 +5273,11 @@
       <c r="E187" t="n">
         <v>118</v>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>094.00118</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4364,6 +5299,11 @@
       <c r="E188" t="n">
         <v>121</v>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>094.00121</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4385,6 +5325,11 @@
       <c r="E189" t="n">
         <v>122</v>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>094.00122</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4406,6 +5351,11 @@
       <c r="E190" t="n">
         <v>136</v>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>094.00136</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4427,6 +5377,11 @@
       <c r="E191" t="n">
         <v>137</v>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>094.00137</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4448,6 +5403,11 @@
       <c r="E192" t="n">
         <v>143</v>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>094.00143</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4469,6 +5429,11 @@
       <c r="E193" t="n">
         <v>145</v>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>094.00145</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4490,6 +5455,11 @@
       <c r="E194" t="n">
         <v>146</v>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>094.00146</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4511,6 +5481,11 @@
       <c r="E195" t="n">
         <v>204</v>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>094.00204</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4532,6 +5507,11 @@
       <c r="E196" t="n">
         <v>213</v>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>094.00213</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4553,6 +5533,11 @@
       <c r="E197" t="n">
         <v>302</v>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>094.00302</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4574,6 +5559,11 @@
       <c r="E198" t="n">
         <v>336</v>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>094.00336</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4595,6 +5585,11 @@
       <c r="E199" t="n">
         <v>337</v>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>094.00337</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4616,6 +5611,11 @@
       <c r="E200" t="n">
         <v>409</v>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>094.00409</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4637,6 +5637,11 @@
       <c r="E201" t="n">
         <v>413</v>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>094.00413</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4658,6 +5663,11 @@
       <c r="E202" t="n">
         <v>436</v>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>094.00436</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4679,6 +5689,11 @@
       <c r="E203" t="n">
         <v>509</v>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>094.00509</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4700,6 +5715,11 @@
       <c r="E204" t="n">
         <v>636</v>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>094.00636</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4721,6 +5741,11 @@
       <c r="E205" t="n">
         <v>641</v>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>094.00641</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4742,6 +5767,11 @@
       <c r="E206" t="n">
         <v>1</v>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>095.00001</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4763,6 +5793,11 @@
       <c r="E207" t="n">
         <v>29</v>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>095.00029</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -4784,6 +5819,11 @@
       <c r="E208" t="n">
         <v>38</v>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>095.00038</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -4805,6 +5845,11 @@
       <c r="E209" t="n">
         <v>28</v>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>097.00028</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -4826,6 +5871,11 @@
       <c r="E210" t="n">
         <v>39</v>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>097.00039</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -4847,6 +5897,11 @@
       <c r="E211" t="n">
         <v>67</v>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>097.00067</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -4868,6 +5923,11 @@
       <c r="E212" t="n">
         <v>78</v>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>097.00078</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -4889,6 +5949,11 @@
       <c r="E213" t="n">
         <v>5</v>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>098.00005</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -4910,6 +5975,11 @@
       <c r="E214" t="n">
         <v>48</v>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>098.00048</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4931,6 +6001,11 @@
       <c r="E215" t="n">
         <v>63</v>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>098.00063</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4952,6 +6027,11 @@
       <c r="E216" t="n">
         <v>65</v>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>098.00065</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -4973,6 +6053,11 @@
       <c r="E217" t="n">
         <v>67</v>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>098.00067</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -4994,6 +6079,11 @@
       <c r="E218" t="n">
         <v>117</v>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>100.00117</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5015,6 +6105,11 @@
       <c r="E219" t="n">
         <v>52</v>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>101.00052</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5036,6 +6131,11 @@
       <c r="E220" t="n">
         <v>174</v>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>101.00174</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5057,6 +6157,11 @@
       <c r="E221" t="n">
         <v>264</v>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>101.00264</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5078,6 +6183,11 @@
       <c r="E222" t="n">
         <v>9</v>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>104.00009</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5099,6 +6209,11 @@
       <c r="E223" t="n">
         <v>32</v>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>104.00032</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5120,6 +6235,11 @@
       <c r="E224" t="n">
         <v>37</v>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>104.00037</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -5141,6 +6261,11 @@
       <c r="E225" t="n">
         <v>39</v>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>104.00039</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -5162,6 +6287,11 @@
       <c r="E226" t="n">
         <v>53</v>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>104.00053</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -5183,6 +6313,11 @@
       <c r="E227" t="n">
         <v>64</v>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>104.00064</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -5204,6 +6339,11 @@
       <c r="E228" t="n">
         <v>75</v>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>104.00075</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5225,6 +6365,11 @@
       <c r="E229" t="n">
         <v>78</v>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>104.00078</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5246,6 +6391,11 @@
       <c r="E230" t="n">
         <v>86</v>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>104.00086</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5267,6 +6417,11 @@
       <c r="E231" t="n">
         <v>92</v>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>104.00092</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5288,6 +6443,11 @@
       <c r="E232" t="n">
         <v>98</v>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>104.00098</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5309,6 +6469,11 @@
       <c r="E233" t="n">
         <v>99</v>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>104.00099</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5330,6 +6495,11 @@
       <c r="E234" t="n">
         <v>287</v>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>104.00287</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5351,6 +6521,11 @@
       <c r="E235" t="n">
         <v>299</v>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>104.00299</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5372,6 +6547,11 @@
       <c r="E236" t="n">
         <v>619</v>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>104.00619</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5393,6 +6573,11 @@
       <c r="E237" t="n">
         <v>633</v>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>104.00633</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5414,6 +6599,11 @@
       <c r="E238" t="n">
         <v>641</v>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>104.00641</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5435,6 +6625,11 @@
       <c r="E239" t="n">
         <v>642</v>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>104.00642</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5456,6 +6651,11 @@
       <c r="E240" t="n">
         <v>746</v>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>104.00746</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5477,6 +6677,11 @@
       <c r="E241" t="n">
         <v>754</v>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>104.00754</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -5498,6 +6703,11 @@
       <c r="E242" t="n">
         <v>758</v>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>104.00758</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -5519,6 +6729,11 @@
       <c r="E243" t="n">
         <v>772</v>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>104.00772</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -5540,6 +6755,11 @@
       <c r="E244" t="n">
         <v>779</v>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>104.00779</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -5561,6 +6781,11 @@
       <c r="E245" t="n">
         <v>788</v>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>104.00788</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -5582,6 +6807,11 @@
       <c r="E246" t="n">
         <v>797</v>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>104.00797</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -5603,6 +6833,11 @@
       <c r="E247" t="n">
         <v>861</v>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>104.00861</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -5624,6 +6859,11 @@
       <c r="E248" t="n">
         <v>876</v>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>104.00876</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -5645,6 +6885,11 @@
       <c r="E249" t="n">
         <v>889</v>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>104.00889</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -5666,6 +6911,11 @@
       <c r="E250" t="n">
         <v>962</v>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>104.00962</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -5687,6 +6937,11 @@
       <c r="E251" t="n">
         <v>963</v>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>104.00963</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -5708,6 +6963,11 @@
       <c r="E252" t="n">
         <v>981</v>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>104.00981</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -5729,6 +6989,11 @@
       <c r="E253" t="n">
         <v>984</v>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>104.00984</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -5750,6 +7015,11 @@
       <c r="E254" t="n">
         <v>986</v>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>104.00986</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -5771,6 +7041,11 @@
       <c r="E255" t="n">
         <v>987</v>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>104.00987</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -5792,6 +7067,11 @@
       <c r="E256" t="n">
         <v>1022</v>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>104.01022</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -5813,6 +7093,11 @@
       <c r="E257" t="n">
         <v>1074</v>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>104.01074</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -5834,6 +7119,11 @@
       <c r="E258" t="n">
         <v>1076</v>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>104.01076</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -5855,6 +7145,11 @@
       <c r="E259" t="n">
         <v>1086</v>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>104.01086</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -5876,6 +7171,11 @@
       <c r="E260" t="n">
         <v>1088</v>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>104.01088</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -5897,6 +7197,11 @@
       <c r="E261" t="n">
         <v>1166</v>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>104.01166</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -5918,6 +7223,11 @@
       <c r="E262" t="n">
         <v>1192</v>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>104.01192</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -5939,6 +7249,11 @@
       <c r="E263" t="n">
         <v>1</v>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>105.00001</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -5960,6 +7275,11 @@
       <c r="E264" t="n">
         <v>9</v>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>105.00009</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -5981,6 +7301,11 @@
       <c r="E265" t="n">
         <v>18</v>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>105.00018</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -6002,6 +7327,11 @@
       <c r="E266" t="n">
         <v>18</v>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>105.00018</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -6023,6 +7353,11 @@
       <c r="E267" t="n">
         <v>26</v>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>105.00026</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -6044,6 +7379,11 @@
       <c r="E268" t="n">
         <v>35</v>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>105.00035</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -6065,6 +7405,11 @@
       <c r="E269" t="n">
         <v>54</v>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>105.00054</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -6086,6 +7431,11 @@
       <c r="E270" t="n">
         <v>83</v>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>105.00083</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -6107,6 +7457,11 @@
       <c r="E271" t="n">
         <v>86</v>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>105.00086</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6128,6 +7483,11 @@
       <c r="E272" t="n">
         <v>92</v>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>105.00092</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -6149,6 +7509,11 @@
       <c r="E273" t="n">
         <v>113</v>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>105.00113</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -6170,6 +7535,11 @@
       <c r="E274" t="n">
         <v>116</v>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>105.00116</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -6191,6 +7561,11 @@
       <c r="E275" t="n">
         <v>117</v>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>105.00117</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -6212,6 +7587,11 @@
       <c r="E276" t="n">
         <v>155</v>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>105.00155</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -6233,6 +7613,11 @@
       <c r="E277" t="n">
         <v>162</v>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>105.00162</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -6254,6 +7639,11 @@
       <c r="E278" t="n">
         <v>163</v>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>105.00163</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -6275,6 +7665,11 @@
       <c r="E279" t="n">
         <v>173</v>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>105.00173</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -6296,6 +7691,11 @@
       <c r="E280" t="n">
         <v>175</v>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>105.00175</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -6317,6 +7717,11 @@
       <c r="E281" t="n">
         <v>186</v>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>105.00186</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -6338,6 +7743,11 @@
       <c r="E282" t="n">
         <v>199</v>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>105.00199</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -6359,6 +7769,11 @@
       <c r="E283" t="n">
         <v>206</v>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>105.00206</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -6380,6 +7795,11 @@
       <c r="E284" t="n">
         <v>214</v>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>105.00214</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -6401,6 +7821,11 @@
       <c r="E285" t="n">
         <v>218</v>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>105.00218</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -6422,6 +7847,11 @@
       <c r="E286" t="n">
         <v>231</v>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>105.00231</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -6443,6 +7873,11 @@
       <c r="E287" t="n">
         <v>236</v>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>105.00236</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -6464,6 +7899,11 @@
       <c r="E288" t="n">
         <v>39</v>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>106.00039</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -6485,6 +7925,11 @@
       <c r="E289" t="n">
         <v>85</v>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>106.00085</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -6506,6 +7951,11 @@
       <c r="E290" t="n">
         <v>104</v>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>106.00104</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -6527,6 +7977,11 @@
       <c r="E291" t="n">
         <v>105</v>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>106.00105</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -6548,6 +8003,11 @@
       <c r="E292" t="n">
         <v>274</v>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>106.00274</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -6569,6 +8029,11 @@
       <c r="E293" t="n">
         <v>282</v>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>106.00282</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -6590,6 +8055,11 @@
       <c r="E294" t="n">
         <v>436</v>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>106.00436</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -6611,6 +8081,11 @@
       <c r="E295" t="n">
         <v>489</v>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>106.00489</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -6632,6 +8107,11 @@
       <c r="E296" t="n">
         <v>528</v>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>106.00528</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -6653,6 +8133,11 @@
       <c r="E297" t="n">
         <v>592</v>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>106.00592</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -6674,6 +8159,11 @@
       <c r="E298" t="n">
         <v>613</v>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>106.00613</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -6695,6 +8185,11 @@
       <c r="E299" t="n">
         <v>615</v>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>106.00615</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -6716,6 +8211,11 @@
       <c r="E300" t="n">
         <v>717</v>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>106.00717</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -6737,6 +8237,11 @@
       <c r="E301" t="n">
         <v>736</v>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>106.00736</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -6758,6 +8263,11 @@
       <c r="E302" t="n">
         <v>856</v>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>106.00856</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -6779,6 +8289,11 @@
       <c r="E303" t="n">
         <v>884</v>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>106.00884</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -6800,6 +8315,11 @@
       <c r="E304" t="n">
         <v>891</v>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>106.00891</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -6821,6 +8341,11 @@
       <c r="E305" t="n">
         <v>1087</v>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>106.01087</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -6842,6 +8367,11 @@
       <c r="E306" t="n">
         <v>1211</v>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>106.01211</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -6863,6 +8393,11 @@
       <c r="E307" t="n">
         <v>1254</v>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>106.01254</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -6884,6 +8419,11 @@
       <c r="E308" t="n">
         <v>1282</v>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>106.01282</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -6905,6 +8445,11 @@
       <c r="E309" t="n">
         <v>1999</v>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>106.01999</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -6926,6 +8471,11 @@
       <c r="E310" t="n">
         <v>2387</v>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>106.02387</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -6947,6 +8497,11 @@
       <c r="E311" t="n">
         <v>2388</v>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>106.02388</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -6968,6 +8523,11 @@
       <c r="E312" t="n">
         <v>2813</v>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>106.02813</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -6989,6 +8549,11 @@
       <c r="E313" t="n">
         <v>2859</v>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>106.02859</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7010,6 +8575,11 @@
       <c r="E314" t="n">
         <v>2908</v>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>106.02908</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7031,6 +8601,11 @@
       <c r="E315" t="n">
         <v>3114</v>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>106.03114</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -7052,6 +8627,11 @@
       <c r="E316" t="n">
         <v>3192</v>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>106.03192</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -7073,6 +8653,11 @@
       <c r="E317" t="n">
         <v>3284</v>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>106.03284</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -7094,6 +8679,11 @@
       <c r="E318" t="n">
         <v>3314</v>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>106.03314</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -7115,6 +8705,11 @@
       <c r="E319" t="n">
         <v>3386</v>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>106.03386</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -7136,6 +8731,11 @@
       <c r="E320" t="n">
         <v>3924</v>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>106.03924</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -7157,6 +8757,11 @@
       <c r="E321" t="n">
         <v>4042</v>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>106.04042</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -7178,6 +8783,11 @@
       <c r="E322" t="n">
         <v>4185</v>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>106.04185</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -7199,6 +8809,11 @@
       <c r="E323" t="n">
         <v>4186</v>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>106.04186</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -7220,6 +8835,11 @@
       <c r="E324" t="n">
         <v>4241</v>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>106.04241</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -7241,6 +8861,11 @@
       <c r="E325" t="n">
         <v>4274</v>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>106.04274</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -7262,6 +8887,11 @@
       <c r="E326" t="n">
         <v>4287</v>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>106.04287</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -7283,6 +8913,11 @@
       <c r="E327" t="n">
         <v>4308</v>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>106.04308</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -7304,6 +8939,11 @@
       <c r="E328" t="n">
         <v>4359</v>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>106.04359</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -7325,6 +8965,11 @@
       <c r="E329" t="n">
         <v>9871</v>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>106.09871</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -7346,6 +8991,11 @@
       <c r="E330" t="n">
         <v>16857</v>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>106.16857</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7367,6 +9017,11 @@
       <c r="E331" t="n">
         <v>71</v>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>107.00071</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -7388,6 +9043,11 @@
       <c r="E332" t="n">
         <v>126</v>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>107.00126</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -7409,6 +9069,11 @@
       <c r="E333" t="n">
         <v>128</v>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>107.00128</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -7430,6 +9095,11 @@
       <c r="E334" t="n">
         <v>182</v>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>107.00182</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -7451,6 +9121,11 @@
       <c r="E335" t="n">
         <v>46</v>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>108.00046</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -7472,6 +9147,11 @@
       <c r="E336" t="n">
         <v>8</v>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>109.00008</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -7493,6 +9173,11 @@
       <c r="E337" t="n">
         <v>13</v>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>109.00013</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7514,6 +9199,11 @@
       <c r="E338" t="n">
         <v>38</v>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>109.00038</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -7535,6 +9225,11 @@
       <c r="E339" t="n">
         <v>98</v>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>109.00098</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -7556,6 +9251,11 @@
       <c r="E340" t="n">
         <v>1</v>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>110.00001</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -7577,6 +9277,11 @@
       <c r="E341" t="n">
         <v>1</v>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>110.00001</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -7598,6 +9303,11 @@
       <c r="E342" t="n">
         <v>4</v>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>110.00004</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -7619,6 +9329,11 @@
       <c r="E343" t="n">
         <v>5</v>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>110.00005</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -7640,6 +9355,11 @@
       <c r="E344" t="n">
         <v>31</v>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>110.00031</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -7661,6 +9381,11 @@
       <c r="E345" t="n">
         <v>35</v>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>110.00035</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -7682,6 +9407,11 @@
       <c r="E346" t="n">
         <v>41</v>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>110.00041</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -7703,6 +9433,11 @@
       <c r="E347" t="n">
         <v>46</v>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>110.00046</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -7724,6 +9459,11 @@
       <c r="E348" t="n">
         <v>51</v>
       </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>110.00051</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -7745,6 +9485,11 @@
       <c r="E349" t="n">
         <v>52</v>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>110.00052</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -7766,6 +9511,11 @@
       <c r="E350" t="n">
         <v>53</v>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>110.00053</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -7787,6 +9537,11 @@
       <c r="E351" t="n">
         <v>57</v>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>110.00057</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -7808,6 +9563,11 @@
       <c r="E352" t="n">
         <v>71</v>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>110.00071</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -7829,6 +9589,11 @@
       <c r="E353" t="n">
         <v>75</v>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>110.00075</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -7850,6 +9615,11 @@
       <c r="E354" t="n">
         <v>77</v>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>110.00077</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -7871,6 +9641,11 @@
       <c r="E355" t="n">
         <v>138</v>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>110.00138</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -7892,6 +9667,11 @@
       <c r="E356" t="n">
         <v>305</v>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>110.00305</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -7913,6 +9693,11 @@
       <c r="E357" t="n">
         <v>307</v>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>110.00307</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -7934,6 +9719,11 @@
       <c r="E358" t="n">
         <v>308</v>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>110.00308</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -7955,6 +9745,11 @@
       <c r="E359" t="n">
         <v>1</v>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>111.00001</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -7976,6 +9771,11 @@
       <c r="E360" t="n">
         <v>1</v>
       </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>111.00001</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -7997,6 +9797,11 @@
       <c r="E361" t="n">
         <v>2</v>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>111.00002</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -8018,6 +9823,11 @@
       <c r="E362" t="n">
         <v>11</v>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>111.00011</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -8039,6 +9849,11 @@
       <c r="E363" t="n">
         <v>12</v>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>111.00012</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -8060,6 +9875,11 @@
       <c r="E364" t="n">
         <v>13</v>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>111.00013</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -8081,6 +9901,11 @@
       <c r="E365" t="n">
         <v>13</v>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>111.00013</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -8102,6 +9927,11 @@
       <c r="E366" t="n">
         <v>42</v>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>111.00042</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -8123,6 +9953,11 @@
       <c r="E367" t="n">
         <v>55</v>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>111.00055</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -8144,6 +9979,11 @@
       <c r="E368" t="n">
         <v>107</v>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>111.00107</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -8165,6 +10005,11 @@
       <c r="E369" t="n">
         <v>123</v>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>111.00123</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -8186,6 +10031,11 @@
       <c r="E370" t="n">
         <v>128</v>
       </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>111.00128</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -8207,6 +10057,11 @@
       <c r="E371" t="n">
         <v>136</v>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>111.00136</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -8228,6 +10083,11 @@
       <c r="E372" t="n">
         <v>141</v>
       </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>111.00141</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -8249,6 +10109,11 @@
       <c r="E373" t="n">
         <v>403</v>
       </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>111.00403</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -8270,6 +10135,11 @@
       <c r="E374" t="n">
         <v>404</v>
       </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>111.00404</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -8291,6 +10161,11 @@
       <c r="E375" t="n">
         <v>408</v>
       </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>111.00408</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -8312,6 +10187,11 @@
       <c r="E376" t="n">
         <v>503</v>
       </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>111.00503</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -8333,6 +10213,11 @@
       <c r="E377" t="n">
         <v>504</v>
       </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>111.00504</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -8354,6 +10239,11 @@
       <c r="E378" t="n">
         <v>1001</v>
       </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>111.01001</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -8375,6 +10265,11 @@
       <c r="E379" t="n">
         <v>1211</v>
       </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>111.01211</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -8396,6 +10291,11 @@
       <c r="E380" t="n">
         <v>1213</v>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>111.01213</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -8417,6 +10317,11 @@
       <c r="E381" t="n">
         <v>1223</v>
       </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>111.01223</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -8438,6 +10343,11 @@
       <c r="E382" t="n">
         <v>1225</v>
       </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>111.01225</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -8459,6 +10369,11 @@
       <c r="E383" t="n">
         <v>1226</v>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>111.01226</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -8480,6 +10395,11 @@
       <c r="E384" t="n">
         <v>1227</v>
       </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>111.01227</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -8501,6 +10421,11 @@
       <c r="E385" t="n">
         <v>1231</v>
       </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>111.01231</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -8522,6 +10447,11 @@
       <c r="E386" t="n">
         <v>5</v>
       </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>112.00005</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -8543,6 +10473,11 @@
       <c r="E387" t="n">
         <v>7</v>
       </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>112.00007</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -8564,6 +10499,11 @@
       <c r="E388" t="n">
         <v>12</v>
       </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>112.00012</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -8585,6 +10525,11 @@
       <c r="E389" t="n">
         <v>14</v>
       </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>112.00014</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -8606,6 +10551,11 @@
       <c r="E390" t="n">
         <v>25</v>
       </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>112.00025</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -8627,6 +10577,11 @@
       <c r="E391" t="n">
         <v>33</v>
       </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>112.00033</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -8648,6 +10603,11 @@
       <c r="E392" t="n">
         <v>34</v>
       </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>112.00034</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -8669,6 +10629,11 @@
       <c r="E393" t="n">
         <v>34</v>
       </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>112.00034</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -8690,6 +10655,11 @@
       <c r="E394" t="n">
         <v>45</v>
       </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>112.00045</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -8711,6 +10681,11 @@
       <c r="E395" t="n">
         <v>51</v>
       </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>112.00051</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -8732,6 +10707,11 @@
       <c r="E396" t="n">
         <v>55</v>
       </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>112.00055</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -8753,6 +10733,11 @@
       <c r="E397" t="n">
         <v>76</v>
       </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>112.00076</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -8774,6 +10759,11 @@
       <c r="E398" t="n">
         <v>77</v>
       </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>112.00077</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -8795,6 +10785,11 @@
       <c r="E399" t="n">
         <v>91</v>
       </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>112.00091</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -8816,6 +10811,11 @@
       <c r="E400" t="n">
         <v>92</v>
       </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>112.00092</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -8837,6 +10837,11 @@
       <c r="E401" t="n">
         <v>126</v>
       </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>112.00126</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -8858,6 +10863,11 @@
       <c r="E402" t="n">
         <v>133</v>
       </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>112.00133</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -8879,6 +10889,11 @@
       <c r="E403" t="n">
         <v>216</v>
       </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>112.00216</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -8900,6 +10915,11 @@
       <c r="E404" t="n">
         <v>244</v>
       </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>112.00244</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -8921,6 +10941,11 @@
       <c r="E405" t="n">
         <v>252</v>
       </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>112.00252</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -8942,6 +10967,11 @@
       <c r="E406" t="n">
         <v>255</v>
       </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>112.00255</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -8963,6 +10993,11 @@
       <c r="E407" t="n">
         <v>259</v>
       </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>112.00259</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -8984,6 +11019,11 @@
       <c r="E408" t="n">
         <v>266</v>
       </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>112.00266</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -9005,6 +11045,11 @@
       <c r="E409" t="n">
         <v>276</v>
       </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>112.00276</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -9026,6 +11071,11 @@
       <c r="E410" t="n">
         <v>277</v>
       </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>112.00277</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -9047,6 +11097,11 @@
       <c r="E411" t="n">
         <v>331</v>
       </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>112.00331</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -9068,6 +11123,11 @@
       <c r="E412" t="n">
         <v>354</v>
       </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>112.00354</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -9089,6 +11149,11 @@
       <c r="E413" t="n">
         <v>368</v>
       </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>112.00368</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -9110,6 +11175,11 @@
       <c r="E414" t="n">
         <v>389</v>
       </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>112.00389</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -9131,6 +11201,11 @@
       <c r="E415" t="n">
         <v>415</v>
       </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>112.00415</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -9152,6 +11227,11 @@
       <c r="E416" t="n">
         <v>442</v>
       </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>112.00442</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -9173,6 +11253,11 @@
       <c r="E417" t="n">
         <v>443</v>
       </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>112.00443</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -9194,6 +11279,11 @@
       <c r="E418" t="n">
         <v>456</v>
       </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>112.00456</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -9215,6 +11305,11 @@
       <c r="E419" t="n">
         <v>487</v>
       </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>112.00487</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -9236,6 +11331,11 @@
       <c r="E420" t="n">
         <v>488</v>
       </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>112.00488</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -9257,6 +11357,11 @@
       <c r="E421" t="n">
         <v>489</v>
       </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>112.00489</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -9278,6 +11383,11 @@
       <c r="E422" t="n">
         <v>511</v>
       </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>112.00511</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -9299,6 +11409,11 @@
       <c r="E423" t="n">
         <v>512</v>
       </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>112.00512</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -9320,6 +11435,11 @@
       <c r="E424" t="n">
         <v>513</v>
       </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>112.00513</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -9341,6 +11461,11 @@
       <c r="E425" t="n">
         <v>544</v>
       </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>112.00544</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -9362,6 +11487,11 @@
       <c r="E426" t="n">
         <v>545</v>
       </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>112.00545</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -9383,6 +11513,11 @@
       <c r="E427" t="n">
         <v>546</v>
       </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>112.00546</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -9404,6 +11539,11 @@
       <c r="E428" t="n">
         <v>551</v>
       </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>112.00551</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -9425,6 +11565,11 @@
       <c r="E429" t="n">
         <v>566</v>
       </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>112.00566</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -9446,6 +11591,11 @@
       <c r="E430" t="n">
         <v>583</v>
       </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>112.00583</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -9467,6 +11617,11 @@
       <c r="E431" t="n">
         <v>601</v>
       </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>112.00601</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -9488,6 +11643,11 @@
       <c r="E432" t="n">
         <v>607</v>
       </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>112.00607</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -9509,6 +11669,11 @@
       <c r="E433" t="n">
         <v>634</v>
       </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>112.00634</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -9530,6 +11695,11 @@
       <c r="E434" t="n">
         <v>685</v>
       </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>112.00685</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -9551,6 +11721,11 @@
       <c r="E435" t="n">
         <v>686</v>
       </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>112.00686</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -9572,6 +11747,11 @@
       <c r="E436" t="n">
         <v>689</v>
       </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>112.00689</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -9593,6 +11773,11 @@
       <c r="E437" t="n">
         <v>697</v>
       </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>112.00697</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -9614,6 +11799,11 @@
       <c r="E438" t="n">
         <v>727</v>
       </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>112.00727</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -9635,6 +11825,11 @@
       <c r="E439" t="n">
         <v>741</v>
       </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>112.00741</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -9656,6 +11851,11 @@
       <c r="E440" t="n">
         <v>742</v>
       </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>112.00742</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -9677,6 +11877,11 @@
       <c r="E441" t="n">
         <v>766</v>
       </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>112.00766</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -9698,6 +11903,11 @@
       <c r="E442" t="n">
         <v>787</v>
       </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>112.00787</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -9719,6 +11929,11 @@
       <c r="E443" t="n">
         <v>793</v>
       </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>112.00793</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -9740,6 +11955,11 @@
       <c r="E444" t="n">
         <v>868</v>
       </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>112.00868</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -9761,6 +11981,11 @@
       <c r="E445" t="n">
         <v>1113</v>
       </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>112.01113</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -9782,6 +12007,11 @@
       <c r="E446" t="n">
         <v>1116</v>
       </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>112.01116</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -9803,6 +12033,11 @@
       <c r="E447" t="n">
         <v>1117</v>
       </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>112.01117</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -9824,6 +12059,11 @@
       <c r="E448" t="n">
         <v>1223</v>
       </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>112.01223</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -9845,6 +12085,11 @@
       <c r="E449" t="n">
         <v>42</v>
       </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>113.00042</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -9866,6 +12111,11 @@
       <c r="E450" t="n">
         <v>17</v>
       </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>115.00017</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -9887,6 +12137,11 @@
       <c r="E451" t="n">
         <v>11</v>
       </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>116.00011</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -9908,6 +12163,11 @@
       <c r="E452" t="n">
         <v>35</v>
       </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>116.00035</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -9929,6 +12189,11 @@
       <c r="E453" t="n">
         <v>36</v>
       </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>116.00036</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -9950,6 +12215,11 @@
       <c r="E454" t="n">
         <v>85</v>
       </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>116.00085</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -9971,6 +12241,11 @@
       <c r="E455" t="n">
         <v>2</v>
       </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>117.00002</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -9992,6 +12267,11 @@
       <c r="E456" t="n">
         <v>3</v>
       </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>117.00003</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -10013,6 +12293,11 @@
       <c r="E457" t="n">
         <v>4</v>
       </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>117.00004</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -10034,6 +12319,11 @@
       <c r="E458" t="n">
         <v>6</v>
       </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>117.00006</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -10055,6 +12345,11 @@
       <c r="E459" t="n">
         <v>7</v>
       </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>117.00007</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -10076,6 +12371,11 @@
       <c r="E460" t="n">
         <v>202</v>
       </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>117.00202</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -10097,6 +12397,11 @@
       <c r="E461" t="n">
         <v>206</v>
       </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>117.00206</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -10118,6 +12423,11 @@
       <c r="E462" t="n">
         <v>2</v>
       </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>119.00002</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -10139,6 +12449,11 @@
       <c r="E463" t="n">
         <v>1002</v>
       </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>121.01002</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -10160,6 +12475,11 @@
       <c r="E464" t="n">
         <v>1003</v>
       </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>121.01003</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -10181,6 +12501,11 @@
       <c r="E465" t="n">
         <v>1004</v>
       </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>121.01004</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -10202,6 +12527,11 @@
       <c r="E466" t="n">
         <v>1005</v>
       </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>121.01005</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -10223,6 +12553,11 @@
       <c r="E467" t="n">
         <v>1007</v>
       </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>121.01007</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -10244,6 +12579,11 @@
       <c r="E468" t="n">
         <v>1</v>
       </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>123.00001</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -10265,6 +12605,11 @@
       <c r="E469" t="n">
         <v>1</v>
       </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>123.00001</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -10286,6 +12631,11 @@
       <c r="E470" t="n">
         <v>9</v>
       </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>123.00009</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -10307,6 +12657,11 @@
       <c r="E471" t="n">
         <v>11</v>
       </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>123.00011</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -10328,6 +12683,11 @@
       <c r="E472" t="n">
         <v>12</v>
       </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>123.00012</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -10349,6 +12709,11 @@
       <c r="E473" t="n">
         <v>31</v>
       </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>123.00031</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -10370,6 +12735,11 @@
       <c r="E474" t="n">
         <v>32</v>
       </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>123.00032</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -10391,6 +12761,11 @@
       <c r="E475" t="n">
         <v>35</v>
       </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>123.00035</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -10412,6 +12787,11 @@
       <c r="E476" t="n">
         <v>37</v>
       </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>123.00037</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -10433,6 +12813,11 @@
       <c r="E477" t="n">
         <v>38</v>
       </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>123.00038</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -10454,6 +12839,11 @@
       <c r="E478" t="n">
         <v>91</v>
       </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>123.00091</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -10475,6 +12865,11 @@
       <c r="E479" t="n">
         <v>105</v>
       </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>123.00105</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -10496,6 +12891,11 @@
       <c r="E480" t="n">
         <v>108</v>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>123.00108</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -10517,6 +12917,11 @@
       <c r="E481" t="n">
         <v>109</v>
       </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>123.00109</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -10538,6 +12943,11 @@
       <c r="E482" t="n">
         <v>111</v>
       </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>123.00111</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -10559,6 +12969,11 @@
       <c r="E483" t="n">
         <v>113</v>
       </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>123.00113</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -10580,6 +12995,11 @@
       <c r="E484" t="n">
         <v>116</v>
       </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>123.00116</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -10601,6 +13021,11 @@
       <c r="E485" t="n">
         <v>117</v>
       </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>123.00117</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -10622,6 +13047,11 @@
       <c r="E486" t="n">
         <v>118</v>
       </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>123.00118</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -10643,6 +13073,11 @@
       <c r="E487" t="n">
         <v>119</v>
       </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>123.00119</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -10664,6 +13099,11 @@
       <c r="E488" t="n">
         <v>122</v>
       </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>123.00122</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -10685,6 +13125,11 @@
       <c r="E489" t="n">
         <v>123</v>
       </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>123.00123</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -10706,6 +13151,11 @@
       <c r="E490" t="n">
         <v>6</v>
       </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>125.00006</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -10727,6 +13177,11 @@
       <c r="E491" t="n">
         <v>53</v>
       </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>125.00053</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -10748,6 +13203,11 @@
       <c r="E492" t="n">
         <v>85</v>
       </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>125.00085</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -10769,6 +13229,11 @@
       <c r="E493" t="n">
         <v>183</v>
       </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>125.00183</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -10790,6 +13255,11 @@
       <c r="E494" t="n">
         <v>7</v>
       </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>127.00007</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -10811,6 +13281,11 @@
       <c r="E495" t="n">
         <v>1</v>
       </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>130.00001</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -10832,6 +13307,11 @@
       <c r="E496" t="n">
         <v>1</v>
       </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>130.00001</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -10853,6 +13333,11 @@
       <c r="E497" t="n">
         <v>2</v>
       </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>130.00002</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -10874,6 +13359,11 @@
       <c r="E498" t="n">
         <v>2</v>
       </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>130.00002</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -10895,6 +13385,11 @@
       <c r="E499" t="n">
         <v>3</v>
       </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>130.00003</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -10916,6 +13411,11 @@
       <c r="E500" t="n">
         <v>4</v>
       </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>130.00004</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -10937,6 +13437,11 @@
       <c r="E501" t="n">
         <v>5</v>
       </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>130.00005</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -10958,6 +13463,11 @@
       <c r="E502" t="n">
         <v>5</v>
       </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>130.00005</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -10979,6 +13489,11 @@
       <c r="E503" t="n">
         <v>6</v>
       </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>130.00006</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -11000,6 +13515,11 @@
       <c r="E504" t="n">
         <v>6</v>
       </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>130.00006</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -11021,6 +13541,11 @@
       <c r="E505" t="n">
         <v>7</v>
       </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>130.00007</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -11042,6 +13567,11 @@
       <c r="E506" t="n">
         <v>8</v>
       </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>130.00008</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -11063,6 +13593,11 @@
       <c r="E507" t="n">
         <v>9</v>
       </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>130.00009</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -11084,6 +13619,11 @@
       <c r="E508" t="n">
         <v>11</v>
       </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>130.00011</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -11105,6 +13645,11 @@
       <c r="E509" t="n">
         <v>12</v>
       </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>130.00012</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -11126,6 +13671,11 @@
       <c r="E510" t="n">
         <v>14</v>
       </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>130.00014</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -11147,6 +13697,11 @@
       <c r="E511" t="n">
         <v>15</v>
       </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>130.00015</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -11168,6 +13723,11 @@
       <c r="E512" t="n">
         <v>16</v>
       </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>130.00016</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -11189,6 +13749,11 @@
       <c r="E513" t="n">
         <v>17</v>
       </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>130.00017</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -11210,6 +13775,11 @@
       <c r="E514" t="n">
         <v>18</v>
       </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>130.00018</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -11231,6 +13801,11 @@
       <c r="E515" t="n">
         <v>19</v>
       </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>130.00019</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -11252,6 +13827,11 @@
       <c r="E516" t="n">
         <v>21</v>
       </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>130.00021</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -11273,6 +13853,11 @@
       <c r="E517" t="n">
         <v>21</v>
       </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>130.00021</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -11294,6 +13879,11 @@
       <c r="E518" t="n">
         <v>22</v>
       </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>130.00022</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -11315,6 +13905,11 @@
       <c r="E519" t="n">
         <v>23</v>
       </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>130.00023</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -11336,6 +13931,11 @@
       <c r="E520" t="n">
         <v>23</v>
       </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>130.00023</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -11357,6 +13957,11 @@
       <c r="E521" t="n">
         <v>24</v>
       </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>130.00024</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -11378,6 +13983,11 @@
       <c r="E522" t="n">
         <v>25</v>
       </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>130.00025</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -11399,6 +14009,11 @@
       <c r="E523" t="n">
         <v>26</v>
       </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>130.00026</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -11420,6 +14035,11 @@
       <c r="E524" t="n">
         <v>26</v>
       </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>130.00026</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -11441,6 +14061,11 @@
       <c r="E525" t="n">
         <v>27</v>
       </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>130.00027</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -11462,6 +14087,11 @@
       <c r="E526" t="n">
         <v>27</v>
       </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>130.00027</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -11483,6 +14113,11 @@
       <c r="E527" t="n">
         <v>28</v>
       </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>130.00028</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -11504,6 +14139,11 @@
       <c r="E528" t="n">
         <v>28</v>
       </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>130.00028</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -11525,6 +14165,11 @@
       <c r="E529" t="n">
         <v>29</v>
       </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>130.00029</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -11546,6 +14191,11 @@
       <c r="E530" t="n">
         <v>29</v>
       </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>130.00029</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -11567,6 +14217,11 @@
       <c r="E531" t="n">
         <v>44</v>
       </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>130.00044</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -11588,6 +14243,11 @@
       <c r="E532" t="n">
         <v>51</v>
       </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>130.00051</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -11609,6 +14269,11 @@
       <c r="E533" t="n">
         <v>57</v>
       </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>130.00057</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -11630,6 +14295,11 @@
       <c r="E534" t="n">
         <v>59</v>
       </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>130.00059</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -11651,6 +14321,11 @@
       <c r="E535" t="n">
         <v>62</v>
       </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>130.00062</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -11672,6 +14347,11 @@
       <c r="E536" t="n">
         <v>63</v>
       </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>130.00063</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -11693,6 +14373,11 @@
       <c r="E537" t="n">
         <v>64</v>
       </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>130.00064</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -11714,6 +14399,11 @@
       <c r="E538" t="n">
         <v>65</v>
       </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>130.00065</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -11735,6 +14425,11 @@
       <c r="E539" t="n">
         <v>85</v>
       </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>130.00085</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -11756,6 +14451,11 @@
       <c r="E540" t="n">
         <v>122</v>
       </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>130.00122</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -11777,6 +14477,11 @@
       <c r="E541" t="n">
         <v>201</v>
       </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>130.00201</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -11798,6 +14503,11 @@
       <c r="E542" t="n">
         <v>202</v>
       </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>130.00202</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -11819,6 +14529,11 @@
       <c r="E543" t="n">
         <v>203</v>
       </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>130.00203</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -11840,6 +14555,11 @@
       <c r="E544" t="n">
         <v>204</v>
       </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>130.00204</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -11861,6 +14581,11 @@
       <c r="E545" t="n">
         <v>205</v>
       </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>130.00205</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -11882,6 +14607,11 @@
       <c r="E546" t="n">
         <v>206</v>
       </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>130.00206</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -11903,6 +14633,11 @@
       <c r="E547" t="n">
         <v>207</v>
       </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>130.00207</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -11924,6 +14659,11 @@
       <c r="E548" t="n">
         <v>208</v>
       </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>130.00208</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -11945,6 +14685,11 @@
       <c r="E549" t="n">
         <v>209</v>
       </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>130.00209</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -11966,6 +14711,11 @@
       <c r="E550" t="n">
         <v>211</v>
       </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>130.00211</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -11987,6 +14737,11 @@
       <c r="E551" t="n">
         <v>212</v>
       </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>130.00212</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -12008,6 +14763,11 @@
       <c r="E552" t="n">
         <v>213</v>
       </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>130.00213</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -12029,6 +14789,11 @@
       <c r="E553" t="n">
         <v>221</v>
       </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>130.00221</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -12050,6 +14815,11 @@
       <c r="E554" t="n">
         <v>222</v>
       </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>130.00222</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -12071,6 +14841,11 @@
       <c r="E555" t="n">
         <v>223</v>
       </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>130.00223</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -12092,6 +14867,11 @@
       <c r="E556" t="n">
         <v>224</v>
       </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>130.00224</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -12113,6 +14893,11 @@
       <c r="E557" t="n">
         <v>225</v>
       </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>130.00225</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -12134,6 +14919,11 @@
       <c r="E558" t="n">
         <v>226</v>
       </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>130.00226</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -12155,6 +14945,11 @@
       <c r="E559" t="n">
         <v>227</v>
       </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>130.00227</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -12176,6 +14971,11 @@
       <c r="E560" t="n">
         <v>228</v>
       </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>130.00228</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -12197,6 +14997,11 @@
       <c r="E561" t="n">
         <v>229</v>
       </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>130.00229</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -12218,6 +15023,11 @@
       <c r="E562" t="n">
         <v>232</v>
       </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>130.00232</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -12239,6 +15049,11 @@
       <c r="E563" t="n">
         <v>233</v>
       </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>130.00233</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -12260,6 +15075,11 @@
       <c r="E564" t="n">
         <v>234</v>
       </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>130.00234</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -12281,6 +15101,11 @@
       <c r="E565" t="n">
         <v>252</v>
       </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>130.00252</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -12302,6 +15127,11 @@
       <c r="E566" t="n">
         <v>253</v>
       </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>130.00253</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -12323,6 +15153,11 @@
       <c r="E567" t="n">
         <v>254</v>
       </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>130.00254</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -12344,6 +15179,11 @@
       <c r="E568" t="n">
         <v>255</v>
       </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>130.00255</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -12365,6 +15205,11 @@
       <c r="E569" t="n">
         <v>261</v>
       </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>130.00261</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -12386,6 +15231,11 @@
       <c r="E570" t="n">
         <v>262</v>
       </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>130.00262</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -12407,6 +15257,11 @@
       <c r="E571" t="n">
         <v>263</v>
       </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>130.00263</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -12428,6 +15283,11 @@
       <c r="E572" t="n">
         <v>264</v>
       </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>130.00264</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -12449,6 +15309,11 @@
       <c r="E573" t="n">
         <v>265</v>
       </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>130.00265</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -12470,6 +15335,11 @@
       <c r="E574" t="n">
         <v>266</v>
       </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>130.00266</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -12491,6 +15361,11 @@
       <c r="E575" t="n">
         <v>267</v>
       </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>130.00267</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -12512,6 +15387,11 @@
       <c r="E576" t="n">
         <v>268</v>
       </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>130.00268</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -12533,6 +15413,11 @@
       <c r="E577" t="n">
         <v>271</v>
       </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>130.00271</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -12554,6 +15439,11 @@
       <c r="E578" t="n">
         <v>272</v>
       </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>130.00272</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -12575,6 +15465,11 @@
       <c r="E579" t="n">
         <v>273</v>
       </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>130.00273</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -12596,6 +15491,11 @@
       <c r="E580" t="n">
         <v>274</v>
       </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>130.00274</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -12617,6 +15517,11 @@
       <c r="E581" t="n">
         <v>275</v>
       </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>130.00275</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -12638,6 +15543,11 @@
       <c r="E582" t="n">
         <v>276</v>
       </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>130.00276</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -12659,6 +15569,11 @@
       <c r="E583" t="n">
         <v>277</v>
       </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>130.00277</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -12680,6 +15595,11 @@
       <c r="E584" t="n">
         <v>278</v>
       </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>130.00278</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -12701,6 +15621,11 @@
       <c r="E585" t="n">
         <v>281</v>
       </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>130.00281</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -12722,6 +15647,11 @@
       <c r="E586" t="n">
         <v>282</v>
       </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>130.00282</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -12743,6 +15673,11 @@
       <c r="E587" t="n">
         <v>283</v>
       </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>130.00283</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -12764,6 +15699,11 @@
       <c r="E588" t="n">
         <v>284</v>
       </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>130.00284</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -12785,6 +15725,11 @@
       <c r="E589" t="n">
         <v>285</v>
       </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>130.00285</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -12806,6 +15751,11 @@
       <c r="E590" t="n">
         <v>286</v>
       </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>130.00286</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -12827,6 +15777,11 @@
       <c r="E591" t="n">
         <v>287</v>
       </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>130.00287</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -12848,6 +15803,11 @@
       <c r="E592" t="n">
         <v>288</v>
       </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>130.00288</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -12869,6 +15829,11 @@
       <c r="E593" t="n">
         <v>289</v>
       </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>130.00289</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -12890,6 +15855,11 @@
       <c r="E594" t="n">
         <v>5</v>
       </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>132.00005</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -12911,6 +15881,11 @@
       <c r="E595" t="n">
         <v>34</v>
       </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>132.00034</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -12932,6 +15907,11 @@
       <c r="E596" t="n">
         <v>59</v>
       </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>132.00059</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -12953,6 +15933,11 @@
       <c r="E597" t="n">
         <v>71</v>
       </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>132.00071</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -12974,6 +15959,11 @@
       <c r="E598" t="n">
         <v>109</v>
       </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>132.00109</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -12995,6 +15985,11 @@
       <c r="E599" t="n">
         <v>134</v>
       </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>132.00134</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -13016,6 +16011,11 @@
       <c r="E600" t="n">
         <v>182</v>
       </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>132.00182</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -13037,6 +16037,11 @@
       <c r="E601" t="n">
         <v>196</v>
       </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>132.00196</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -13058,6 +16063,11 @@
       <c r="E602" t="n">
         <v>197</v>
       </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>132.00197</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -13079,6 +16089,11 @@
       <c r="E603" t="n">
         <v>215</v>
       </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>132.00215</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -13100,6 +16115,11 @@
       <c r="E604" t="n">
         <v>298</v>
       </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>132.00298</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -13121,6 +16141,11 @@
       <c r="E605" t="n">
         <v>346</v>
       </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>132.00346</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -13142,6 +16167,11 @@
       <c r="E606" t="n">
         <v>501</v>
       </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>132.00501</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -13163,6 +16193,11 @@
       <c r="E607" t="n">
         <v>573</v>
       </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>132.00573</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -13184,6 +16219,11 @@
       <c r="E608" t="n">
         <v>612</v>
       </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>132.00612</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -13205,6 +16245,11 @@
       <c r="E609" t="n">
         <v>707</v>
       </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>132.00707</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -13226,6 +16271,11 @@
       <c r="E610" t="n">
         <v>722</v>
       </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>132.00722</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -13247,6 +16297,11 @@
       <c r="E611" t="n">
         <v>723</v>
       </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>132.00723</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -13268,6 +16323,11 @@
       <c r="E612" t="n">
         <v>725</v>
       </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>132.00725</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -13289,6 +16349,11 @@
       <c r="E613" t="n">
         <v>1001</v>
       </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>132.01001</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -13310,6 +16375,11 @@
       <c r="E614" t="n">
         <v>1014</v>
       </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>132.01014</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -13331,6 +16401,11 @@
       <c r="E615" t="n">
         <v>2001</v>
       </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>132.02001</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -13352,6 +16427,11 @@
       <c r="E616" t="n">
         <v>2002</v>
       </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>132.02002</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -13373,6 +16453,11 @@
       <c r="E617" t="n">
         <v>2007</v>
       </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>132.02007</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -13394,6 +16479,11 @@
       <c r="E618" t="n">
         <v>7</v>
       </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>134.00007</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -13415,6 +16505,11 @@
       <c r="E619" t="n">
         <v>1</v>
       </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>136.00001</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -13436,6 +16531,11 @@
       <c r="E620" t="n">
         <v>4</v>
       </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>136.00004</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -13457,6 +16557,11 @@
       <c r="E621" t="n">
         <v>38</v>
       </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>136.00038</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -13478,6 +16583,11 @@
       <c r="E622" t="n">
         <v>89</v>
       </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>136.00089</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -13499,6 +16609,11 @@
       <c r="E623" t="n">
         <v>105</v>
       </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>136.00105</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -13520,6 +16635,11 @@
       <c r="E624" t="n">
         <v>138</v>
       </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>136.00138</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -13541,6 +16661,11 @@
       <c r="E625" t="n">
         <v>15</v>
       </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>137.00015</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -13562,6 +16687,11 @@
       <c r="E626" t="n">
         <v>16</v>
       </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>137.00016</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -13583,6 +16713,11 @@
       <c r="E627" t="n">
         <v>17</v>
       </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>137.00017</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -13604,6 +16739,11 @@
       <c r="E628" t="n">
         <v>23</v>
       </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>137.00023</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -13625,6 +16765,11 @@
       <c r="E629" t="n">
         <v>3</v>
       </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>139.00003</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -13646,6 +16791,11 @@
       <c r="E630" t="n">
         <v>7</v>
       </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>139.00007</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -13667,6 +16817,11 @@
       <c r="E631" t="n">
         <v>11</v>
       </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>139.00011</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -13688,6 +16843,11 @@
       <c r="E632" t="n">
         <v>12</v>
       </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>139.00012</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -13709,6 +16869,11 @@
       <c r="E633" t="n">
         <v>13</v>
       </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>139.00013</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -13730,6 +16895,11 @@
       <c r="E634" t="n">
         <v>25</v>
       </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>139.00025</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -13751,6 +16921,11 @@
       <c r="E635" t="n">
         <v>36</v>
       </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>139.00036</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -13772,6 +16947,11 @@
       <c r="E636" t="n">
         <v>73</v>
       </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>139.00073</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -13793,6 +16973,11 @@
       <c r="E637" t="n">
         <v>74</v>
       </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>139.00074</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -13814,6 +16999,11 @@
       <c r="E638" t="n">
         <v>83</v>
       </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>139.00083</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -13835,6 +17025,11 @@
       <c r="E639" t="n">
         <v>84</v>
       </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>139.00084</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -13856,6 +17051,11 @@
       <c r="E640" t="n">
         <v>101</v>
       </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>139.00101</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -13877,6 +17077,11 @@
       <c r="E641" t="n">
         <v>114</v>
       </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>139.00114</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -13898,6 +17103,11 @@
       <c r="E642" t="n">
         <v>85</v>
       </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>145.00085</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -13919,6 +17129,11 @@
       <c r="E643" t="n">
         <v>7</v>
       </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>150.00007</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -13940,6 +17155,11 @@
       <c r="E644" t="n">
         <v>8</v>
       </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>150.00008</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -13961,6 +17181,11 @@
       <c r="E645" t="n">
         <v>9</v>
       </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>150.00009</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -13982,6 +17207,11 @@
       <c r="E646" t="n">
         <v>32</v>
       </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>150.00032</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -14003,6 +17233,11 @@
       <c r="E647" t="n">
         <v>33</v>
       </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>150.00033</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -14024,6 +17259,11 @@
       <c r="E648" t="n">
         <v>6</v>
       </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>157.00006</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -14045,6 +17285,11 @@
       <c r="E649" t="n">
         <v>2</v>
       </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>158.00002</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -14066,6 +17311,11 @@
       <c r="E650" t="n">
         <v>3</v>
       </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>158.00003</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -14087,6 +17337,11 @@
       <c r="E651" t="n">
         <v>77</v>
       </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>201.00077</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -14108,6 +17363,11 @@
       <c r="E652" t="n">
         <v>78</v>
       </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>201.00078</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -14129,6 +17389,11 @@
       <c r="E653" t="n">
         <v>79</v>
       </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>201.00079</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -14150,6 +17415,11 @@
       <c r="E654" t="n">
         <v>81</v>
       </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>201.00081</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -14171,6 +17441,11 @@
       <c r="E655" t="n">
         <v>82</v>
       </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>201.00082</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -14192,6 +17467,11 @@
       <c r="E656" t="n">
         <v>84</v>
       </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>201.00084</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -14213,6 +17493,11 @@
       <c r="E657" t="n">
         <v>85</v>
       </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>201.00085</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -14234,6 +17519,11 @@
       <c r="E658" t="n">
         <v>88</v>
       </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>201.00088</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -14255,6 +17545,11 @@
       <c r="E659" t="n">
         <v>2</v>
       </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>504.00002</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -14276,6 +17571,11 @@
       <c r="E660" t="n">
         <v>3</v>
       </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>506.00003</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -14297,6 +17597,11 @@
       <c r="E661" t="n">
         <v>4</v>
       </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>506.00004</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -14318,6 +17623,11 @@
       <c r="E662" t="n">
         <v>5</v>
       </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>507.00005</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -14339,6 +17649,11 @@
       <c r="E663" t="n">
         <v>18</v>
       </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>507.00018</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -14360,6 +17675,11 @@
       <c r="E664" t="n">
         <v>19</v>
       </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>507.00019</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -14381,6 +17701,11 @@
       <c r="E665" t="n">
         <v>43</v>
       </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>507.00043</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -14402,6 +17727,11 @@
       <c r="E666" t="n">
         <v>49</v>
       </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>507.00049</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -14423,6 +17753,11 @@
       <c r="E667" t="n">
         <v>59</v>
       </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>507.00059</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -14444,6 +17779,11 @@
       <c r="E668" t="n">
         <v>87</v>
       </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>507.00087</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -14465,6 +17805,11 @@
       <c r="E669" t="n">
         <v>97</v>
       </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>507.00097</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -14486,6 +17831,11 @@
       <c r="E670" t="n">
         <v>111</v>
       </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>507.00111</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -14507,6 +17857,11 @@
       <c r="E671" t="n">
         <v>192</v>
       </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>507.00192</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -14528,6 +17883,11 @@
       <c r="E672" t="n">
         <v>195</v>
       </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>507.00195</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -14549,6 +17909,11 @@
       <c r="E673" t="n">
         <v>203</v>
       </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>507.00203</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -14570,6 +17935,11 @@
       <c r="E674" t="n">
         <v>2</v>
       </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>510.00002</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -14591,6 +17961,11 @@
       <c r="E675" t="n">
         <v>4</v>
       </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>510.00004</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -14612,6 +17987,11 @@
       <c r="E676" t="n">
         <v>6</v>
       </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>510.00006</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -14633,6 +18013,11 @@
       <c r="E677" t="n">
         <v>9</v>
       </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>510.00009</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -14654,6 +18039,11 @@
       <c r="E678" t="n">
         <v>82</v>
       </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>510.00082</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -14675,6 +18065,11 @@
       <c r="E679" t="n">
         <v>84</v>
       </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>510.00084</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -14696,6 +18091,11 @@
       <c r="E680" t="n">
         <v>36</v>
       </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>511.00036</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -14717,6 +18117,11 @@
       <c r="E681" t="n">
         <v>71</v>
       </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>511.00071</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -14738,6 +18143,11 @@
       <c r="E682" t="n">
         <v>125</v>
       </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>511.00125</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -14759,6 +18169,11 @@
       <c r="E683" t="n">
         <v>32</v>
       </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>513.00032</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -14780,6 +18195,11 @@
       <c r="E684" t="n">
         <v>57</v>
       </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>513.00057</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -14801,6 +18221,11 @@
       <c r="E685" t="n">
         <v>67</v>
       </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>513.00067</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -14822,6 +18247,11 @@
       <c r="E686" t="n">
         <v>77</v>
       </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>513.00077</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -14843,6 +18273,11 @@
       <c r="E687" t="n">
         <v>2</v>
       </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>515.00002</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -14864,6 +18299,11 @@
       <c r="E688" t="n">
         <v>12</v>
       </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>515.00012</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -14885,6 +18325,11 @@
       <c r="E689" t="n">
         <v>1</v>
       </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>518.00001</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -14906,6 +18351,11 @@
       <c r="E690" t="n">
         <v>2</v>
       </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>518.00002</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -14927,6 +18377,11 @@
       <c r="E691" t="n">
         <v>2</v>
       </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>601.00002</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -14948,6 +18403,11 @@
       <c r="E692" t="n">
         <v>21</v>
       </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>601.00021</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -14969,6 +18429,11 @@
       <c r="E693" t="n">
         <v>22</v>
       </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>601.00022</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -14990,6 +18455,11 @@
       <c r="E694" t="n">
         <v>25</v>
       </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>601.00025</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -15011,6 +18481,11 @@
       <c r="E695" t="n">
         <v>153</v>
       </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>601.00153</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -15032,6 +18507,11 @@
       <c r="E696" t="n">
         <v>173</v>
       </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>601.00173</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -15052,6 +18532,11 @@
       </c>
       <c r="E697" t="n">
         <v>271</v>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>601.00271</t>
+        </is>
       </c>
     </row>
   </sheetData>
